--- a/docs/plantillas/importar-compras.xlsx
+++ b/docs/plantillas/importar-compras.xlsx
@@ -64,9 +64,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -398,115 +397,91 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Y1"/>
-  <cols>
-    <col min="1" max="1" width="16.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="21.83203125" customWidth="1"/>
-    <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="15.83203125" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" customWidth="1"/>
-    <col min="8" max="8" width="16.83203125" customWidth="1"/>
-    <col min="9" max="9" width="19.83203125" customWidth="1"/>
-    <col min="10" max="10" width="17.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="12.83203125" customWidth="1"/>
-    <col min="13" max="13" width="15.83203125" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="12.83203125" customWidth="1"/>
-    <col min="16" max="16" width="13.83203125" customWidth="1"/>
-    <col min="17" max="17" width="12.83203125" customWidth="1"/>
-    <col min="18" max="18" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="25.83203125" customWidth="1"/>
-    <col min="20" max="20" width="19.83203125" customWidth="1"/>
-    <col min="21" max="21" width="12.83203125" customWidth="1"/>
-    <col min="22" max="22" width="12.83203125" customWidth="1"/>
-    <col min="23" max="23" width="12.83203125" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="16.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:Z1"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="str">
+      <c r="A1" t="str">
         <v>TIPO DE COMPRA</v>
       </c>
-      <c r="B1" s="1" t="str">
+      <c r="B1" t="str">
         <v>LÍNEA DE NEGOCIO</v>
       </c>
-      <c r="C1" s="1" t="str">
+      <c r="C1" t="str">
         <v>TIPO DE COMPROBANTE</v>
       </c>
-      <c r="D1" s="1" t="str">
+      <c r="D1" t="str">
         <v>SERIE-NÚMERO</v>
       </c>
-      <c r="E1" s="1" t="str">
+      <c r="E1" t="str">
         <v>FECHA DE EMISIÓN</v>
       </c>
-      <c r="F1" s="1" t="str">
+      <c r="F1" t="str">
         <v>RUC PROVEEDOR</v>
       </c>
-      <c r="G1" s="1" t="str">
+      <c r="G1" t="str">
         <v>MONEDA</v>
       </c>
-      <c r="H1" s="1" t="str">
+      <c r="H1" t="str">
         <v>TIPO DE CAMBIO</v>
       </c>
-      <c r="I1" s="1" t="str">
+      <c r="I1" t="str">
         <v>CONDICIÓN DE PAGO</v>
       </c>
-      <c r="J1" s="1" t="str">
+      <c r="J1" t="str">
         <v>DÍAS DE CRÉDITO</v>
       </c>
-      <c r="K1" s="1" t="str">
+      <c r="K1" t="str">
         <v>TIPO DE SERVICIO</v>
       </c>
-      <c r="L1" s="1" t="str">
+      <c r="L1" t="str">
         <v>TASA IGV</v>
       </c>
-      <c r="M1" s="1" t="str">
+      <c r="M1" t="str">
         <v>OBSERVACIONES</v>
       </c>
-      <c r="N1" s="1" t="str">
-        <v>TOTAL COMPROBANTE</v>
-      </c>
-      <c r="O1" s="1" t="str">
+      <c r="N1" t="str">
+        <v>TOTAL COMPROBANTE CON IGV</v>
+      </c>
+      <c r="O1" t="str">
         <v>SKU</v>
       </c>
-      <c r="P1" s="1" t="str">
+      <c r="P1" t="str">
         <v>DESCRIPCIÓN</v>
       </c>
-      <c r="Q1" s="1" t="str">
+      <c r="Q1" t="str">
         <v>CANTIDAD</v>
       </c>
-      <c r="R1" s="1" t="str">
+      <c r="R1" t="str">
         <v>UNIDAD</v>
       </c>
-      <c r="S1" s="1" t="str">
+      <c r="S1" t="str">
         <v>PRECIO UNITARIO SIN IGV</v>
       </c>
-      <c r="T1" s="1" t="str">
+      <c r="T1" t="str">
+        <v>IMPORTE SIN IGV</v>
+      </c>
+      <c r="U1" t="str">
         <v>CÓDIGO DE ACABADO</v>
       </c>
-      <c r="U1" s="1" t="str">
+      <c r="V1" t="str">
         <v>COLOR</v>
       </c>
-      <c r="V1" s="1" t="str">
+      <c r="W1" t="str">
         <v>ESPESOR MM</v>
       </c>
-      <c r="W1" s="1" t="str">
+      <c r="X1" t="str">
         <v>ANCHO MM</v>
       </c>
-      <c r="X1" s="1" t="str">
+      <c r="Y1" t="str">
         <v>KG</v>
       </c>
-      <c r="Y1" s="1" t="str">
+      <c r="Z1" t="str">
         <v>CÓDIGO EXTERNO</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:Y1"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:Z1"/>
   </ignoredErrors>
 </worksheet>
 </file>